--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB61DCC0-D4E5-4D91-A810-47A914EE7749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4817844-173A-43E3-8B21-1B5E2F565F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="106">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -384,6 +384,70 @@
   </si>
   <si>
     <t>84、85、86、87、88</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32、33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、2、3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、5、6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7、8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9、10、11、12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第2章：1、2、3、4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第3章：1、2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、4、5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、7、8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11、12、13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27、14、15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16、17、18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19、20、21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22、23、24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25、26</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -391,7 +455,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,8 +470,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,7 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -494,10 +584,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -506,10 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -792,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="15.77734375" style="2" customWidth="1"/>
@@ -800,460 +899,585 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="F10" s="7" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="F10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="4">
         <v>43</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="C20" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="B21" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>1</v>
+      </c>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4817844-173A-43E3-8B21-1B5E2F565F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -599,6 +599,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -606,9 +609,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -899,16 +899,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -971,10 +971,10 @@
       <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="10"/>
+      <c r="F4" s="11"/>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
@@ -1052,16 +1052,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
@@ -1208,16 +1208,16 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -1328,22 +1328,22 @@
       <c r="B20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="8" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1351,24 +1351,24 @@
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="8" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="9">
         <v>1</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1398,19 +1398,19 @@
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="8" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1418,13 +1418,13 @@
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="8" t="s">
         <v>105</v>
       </c>
       <c r="E25" s="1"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4817844-173A-43E3-8B21-1B5E2F565F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3643885-3A7D-4D01-AA53-A1011D361FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -942,7 +942,7 @@
       <c r="C3" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3643885-3A7D-4D01-AA53-A1011D361FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5B4E9A-AF9B-4972-AA2B-F656213099C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -945,10 +945,10 @@
       <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5B4E9A-AF9B-4972-AA2B-F656213099C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E28C3AD-2959-41F7-8935-5B30ED473D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -951,7 +951,7 @@
       <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E28C3AD-2959-41F7-8935-5B30ED473D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C15AF7-0F08-4193-B6C1-9EC5A935D954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,7 +954,7 @@
       <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C15AF7-0F08-4193-B6C1-9EC5A935D954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2DE3F9-A00E-4684-9046-099024C30982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -127,10 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>蓝桥杯算法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>55、56、57</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -448,6 +444,10 @@
   </si>
   <si>
     <t>25、26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -605,10 +605,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -940,7 +940,7 @@
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>15</v>
@@ -972,7 +972,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="3" t="s">
@@ -987,25 +987,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1013,25 +1013,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1039,16 +1039,16 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1094,13 +1094,13 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="F10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1111,22 +1111,22 @@
         <v>17</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4">
         <v>43</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1134,25 +1134,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1160,25 +1160,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1186,25 +1186,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1248,25 +1248,25 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1274,25 +1274,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1300,25 +1300,25 @@
         <v>9</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1326,25 +1326,25 @@
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1352,10 +1352,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>97</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1399,19 +1399,19 @@
         <v>7</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1419,13 +1419,13 @@
         <v>8</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2DE3F9-A00E-4684-9046-099024C30982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC83D808-8E72-4D24-B954-5B7D8A76CB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4344" yWindow="204" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -962,7 +962,7 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC83D808-8E72-4D24-B954-5B7D8A76CB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF0644C-7EB5-4153-BEDC-E32E62FE84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4092" yWindow="864" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -965,7 +965,7 @@
       <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF0644C-7EB5-4153-BEDC-E32E62FE84F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63018E2C-F023-4294-950D-219B8464A445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4092" yWindow="864" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -968,14 +968,14 @@
       <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>105</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63018E2C-F023-4294-950D-219B8464A445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7698780-6465-4BFD-AB47-C8BF9FB67184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4092" yWindow="864" windowWidth="16896" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="135">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -443,11 +443,126 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>25、26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>七月 July</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25、26、27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第四章：1、2、3、4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16、17、18、19、20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21、22、23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24、25、26、27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28、29、30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第五章：1、2、3、4、5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、7、8、9、10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第六章：1、2、3、4、5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模拟考试1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段目标：</t>
+  </si>
+  <si>
+    <t>场次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>政治</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.1模拟考试1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注：前X次模考，政治按70分算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.8模拟考试2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>95+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要时间点：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9月前模考达到350+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大四开学前必须完成择校咨询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国庆节之前模考达到370+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考研初试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -455,7 +570,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -472,6 +587,15 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
@@ -523,7 +647,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -546,37 +670,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -602,13 +700,22 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -891,26 +998,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="15.77734375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="9" max="9" width="8.88671875" style="2"/>
+    <col min="10" max="10" width="19.5546875" style="2" customWidth="1"/>
+    <col min="11" max="14" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="11" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="J1" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+    </row>
+    <row r="2" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -933,8 +1052,26 @@
       <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="N2" s="1">
+        <v>408</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +1094,24 @@
       <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O3" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -971,22 +1124,38 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="11"/>
+      <c r="E4" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="14"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="O4" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1007,8 +1176,14 @@
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1208,14 @@
       <c r="H6" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1050,20 +1231,47 @@
       <c r="E7" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="J8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K8" s="1">
+        <v>75</v>
+      </c>
+      <c r="L8" s="1">
+        <v>70</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O8" s="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>0</v>
@@ -1086,13 +1294,23 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+    </row>
+    <row r="10" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="4" t="s">
         <v>42</v>
       </c>
@@ -1102,8 +1320,12 @@
       <c r="H10" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1128,8 +1350,11 @@
       <c r="H11" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1154,8 +1379,11 @@
       <c r="H12" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1180,8 +1408,11 @@
       <c r="H13" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,19 +1438,19 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>0</v>
@@ -1357,18 +1588,23 @@
       <c r="C21" s="8" t="s">
         <v>97</v>
       </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>1</v>
-      </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1398,6 +1634,8 @@
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="8" t="s">
         <v>98</v>
       </c>
@@ -1425,31 +1663,57 @@
         <v>103</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="B26" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -1465,16 +1729,20 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="H28" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="J9:O9"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7698780-6465-4BFD-AB47-C8BF9FB67184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C1D61B-CE58-4DBA-8422-7520156AED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1158,7 +1158,7 @@
       <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C1D61B-CE58-4DBA-8422-7520156AED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A89AF4-4138-4D06-97DF-9163C35DBAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1161,7 +1161,7 @@
       <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A89AF4-4138-4D06-97DF-9163C35DBAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DFDF3F-5767-47B3-B520-F599386AC6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="136">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -563,6 +563,10 @@
   </si>
   <si>
     <t>120+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备考的时间会过得很快的，现在只有246天，五一过完就不到230天，复习个一个月，六月就要应付期末考试（强度会降低）这时候已经剩下不到200天了，等到期末考试应付完，就得开始暑假的强化冲刺（有模拟考，而且要进行初步择校），结束后，估计也就不到120天，120天也就4个月，100天左右就到了国庆和中秋假期了，倒计时100天后就得忙着择校、报名、一周一次模考第话，也就模拟个9次而已，到时候还有政治课要上，得花时间听课、刷题背诵……所以时间是过得很快地，一会就结束了，所以现在200多天看似很多，但是其实只是刚好够用而已，一定一定要撑住不能松懈，当然在完成基本任务之后可以适当休息片刻，但不要放纵地去玩（不要出现考完期末就爽完好几天，放假先玩几天再学习之类的）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -674,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -716,6 +720,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -998,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="15.77734375" style="2" customWidth="1"/>
@@ -1734,8 +1741,21 @@
       </c>
       <c r="H28" s="1"/>
     </row>
+    <row r="37" spans="1:8" ht="122.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
     <mergeCell ref="J9:O9"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DFDF3F-5767-47B3-B520-F599386AC6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E68175-9C84-4F7C-BE63-DF7357EE4C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6972" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -567,6 +567,10 @@
   </si>
   <si>
     <t>备考的时间会过得很快的，现在只有246天，五一过完就不到230天，复习个一个月，六月就要应付期末考试（强度会降低）这时候已经剩下不到200天了，等到期末考试应付完，就得开始暑假的强化冲刺（有模拟考，而且要进行初步择校），结束后，估计也就不到120天，120天也就4个月，100天左右就到了国庆和中秋假期了，倒计时100天后就得忙着择校、报名、一周一次模考第话，也就模拟个9次而已，到时候还有政治课要上，得花时间听课、刷题背诵……所以时间是过得很快地，一会就结束了，所以现在200多天看似很多，但是其实只是刚好够用而已，一定一定要撑住不能松懈，当然在完成基本任务之后可以适当休息片刻，但不要放纵地去玩（不要出现考完期末就爽完好几天，放假先玩几天再学习之类的）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欧几里得小程序模拟考每年从7月开始，每月一次</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +578,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,6 +604,14 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
@@ -678,7 +690,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -708,6 +720,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1017,24 +1032,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="J1" s="12" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="J1" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
     </row>
     <row r="2" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1131,10 +1146,10 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="14"/>
+      <c r="F4" s="15"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
@@ -1171,10 +1186,10 @@
       <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -1249,16 +1264,16 @@
       <c r="O7" s="1"/>
     </row>
     <row r="8" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1301,14 +1316,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1444,18 +1459,22 @@
       <c r="H14" s="6" t="s">
         <v>69</v>
       </c>
+      <c r="J14" s="16" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="15" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -1602,16 +1621,16 @@
       <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1742,19 +1761,19 @@
       <c r="H28" s="1"/>
     </row>
     <row r="37" spans="1:8" ht="122.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -1763,6 +1782,7 @@
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="J14:J15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E68175-9C84-4F7C-BE63-DF7357EE4C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBADD7C9-D4F5-4BFD-A95E-17088E02D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6972" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="197">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -566,11 +566,271 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>备考的时间会过得很快的，现在只有246天，五一过完就不到230天，复习个一个月，六月就要应付期末考试（强度会降低）这时候已经剩下不到200天了，等到期末考试应付完，就得开始暑假的强化冲刺（有模拟考，而且要进行初步择校），结束后，估计也就不到120天，120天也就4个月，100天左右就到了国庆和中秋假期了，倒计时100天后就得忙着择校、报名、一周一次模考第话，也就模拟个9次而已，到时候还有政治课要上，得花时间听课、刷题背诵……所以时间是过得很快地，一会就结束了，所以现在200多天看似很多，但是其实只是刚好够用而已，一定一定要撑住不能松懈，当然在完成基本任务之后可以适当休息片刻，但不要放纵地去玩（不要出现考完期末就爽完好几天，放假先玩几天再学习之类的）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>欧几里得小程序模拟考每年从7月开始，每月一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>复习任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>备考的时间会过得很快的，现在只有246天，五一过完就不到230天，复习个一个月，六月就要应付期末考试（强度会降低）这时候已经剩下不到200天了，等到期末考试应付完，就得开始暑假的强化冲刺（有模拟考，而且要进行初步择校），结束后，估计也就不到120天，120天也就4个月，100天左右就到了国庆和中秋假期了，倒计时100天后就得忙着择校、报名、一周一次模考第话，也就模拟个9次而已，到时候还有政治课要上，得花时间听课、刷题背诵……所以时间是过得很快地，一会就结束了，所以现在200多天看似很多，但是其实只是刚好够用而已，一定一定要撑住不能松懈，当然在完成基本任务之后可以适当休息片刻，但不要放纵地去玩（不要出现考完期末就爽完好几天，放假先玩几天再学习之类的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一章绪论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性表的定义和基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性表的顺序表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性表的链式表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2 队列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1 栈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3 栈和队列的应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4 数组和特殊矩阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第四章 串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二叉树的概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二叉树的遍历和线索二叉树</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树、森林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树和二叉树的应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的存储及基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的遍历</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查找的概念、顺序查找和折半查找</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树形查找</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B树和B+树</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>散列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交换排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归并排序、基数排序和计数排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各种内部排序算法的比较</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机系统概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息、反思、弹性调整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数制与编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运算方法和运算电路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数的表示与运算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储器概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主存储器与CPU的连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高速缓冲存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寻址方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>程序的机器级代码表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CISC和RISC的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU的功能和基本结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令执行过程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据通路的功能和基本结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制器的功能和工作原理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常和中断机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令流水线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多处理器基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总线概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总线事务和定时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I/O系统基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I/O结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I/O方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据结构滚动复习计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机组成原理滚动复习计划</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +838,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,6 +879,13 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -687,10 +957,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -740,9 +1013,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币" xfId="1" builtinId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1020,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:V78"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="15.77734375" style="2" customWidth="1"/>
@@ -1028,10 +1314,16 @@
     <col min="10" max="10" width="19.5546875" style="2" customWidth="1"/>
     <col min="11" max="14" width="8.88671875" style="2"/>
     <col min="15" max="15" width="11" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="2"/>
+    <col min="16" max="17" width="8.88671875" style="2"/>
+    <col min="18" max="18" width="12.88671875" style="18" customWidth="1"/>
+    <col min="19" max="19" width="49.6640625" style="10" customWidth="1"/>
+    <col min="20" max="20" width="12.77734375" style="10" customWidth="1"/>
+    <col min="21" max="21" width="49.6640625" style="10" customWidth="1"/>
+    <col min="22" max="22" width="12.88671875" style="10" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>12</v>
       </c>
@@ -1050,8 +1342,16 @@
       <c r="M1" s="13"/>
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
-    </row>
-    <row r="2" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R1" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="U1" s="17"/>
+    </row>
+    <row r="2" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1092,8 +1392,23 @@
       <c r="O2" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R2" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1132,8 +1447,20 @@
       <c r="O3" s="1">
         <v>315</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R3" s="19">
+        <v>46136</v>
+      </c>
+      <c r="S3" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="T3" s="19">
+        <v>46167</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1172,8 +1499,20 @@
       <c r="O4" s="1">
         <v>325</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R4" s="19">
+        <v>46137</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="T4" s="19">
+        <v>46168</v>
+      </c>
+      <c r="U4" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1192,7 +1531,7 @@
       <c r="F5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -1204,8 +1543,20 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="19">
+        <v>46138</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="T5" s="19">
+        <v>46169</v>
+      </c>
+      <c r="U5" s="10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1236,8 +1587,20 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="19">
+        <v>46139</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="T6" s="19">
+        <v>46170</v>
+      </c>
+      <c r="U6" s="10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1262,8 +1625,20 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R7" s="19">
+        <v>46140</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="T7" s="19">
+        <v>46171</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>13</v>
       </c>
@@ -1292,8 +1667,20 @@
       <c r="O8" s="1">
         <v>395</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R8" s="19">
+        <v>46141</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="T8" s="19">
+        <v>46172</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>0</v>
@@ -1324,8 +1711,20 @@
       <c r="M9" s="14"/>
       <c r="N9" s="14"/>
       <c r="O9" s="14"/>
-    </row>
-    <row r="10" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R9" s="19">
+        <v>46142</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="T9" s="19">
+        <v>46173</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1346,8 +1745,20 @@
         <v>128</v>
       </c>
       <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R10" s="19">
+        <v>46143</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="T10" s="19">
+        <v>46174</v>
+      </c>
+      <c r="U10" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1375,8 +1786,20 @@
       <c r="J11" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R11" s="19">
+        <v>46144</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="T11" s="19">
+        <v>46175</v>
+      </c>
+      <c r="U11" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1404,8 +1827,20 @@
       <c r="J12" s="10" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R12" s="19">
+        <v>46145</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="T12" s="19">
+        <v>46176</v>
+      </c>
+      <c r="U12" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1433,8 +1868,20 @@
       <c r="J13" s="10" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R13" s="19">
+        <v>46146</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="T13" s="19">
+        <v>46177</v>
+      </c>
+      <c r="U13" s="10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1460,10 +1907,22 @@
         <v>69</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="R14" s="19">
+        <v>46147</v>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="T14" s="19">
+        <v>46178</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>14</v>
       </c>
@@ -1475,8 +1934,20 @@
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R15" s="19">
+        <v>46148</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="T15" s="19">
+        <v>46179</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>0</v>
@@ -1499,8 +1970,20 @@
       <c r="H16" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R16" s="19">
+        <v>46149</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="T16" s="19">
+        <v>46180</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -1525,8 +2008,20 @@
       <c r="H17" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R17" s="19">
+        <v>46150</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="T17" s="19">
+        <v>46181</v>
+      </c>
+      <c r="U17" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
@@ -1551,8 +2046,20 @@
       <c r="H18" s="6" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R18" s="19">
+        <v>46151</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="T18" s="19">
+        <v>46182</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
@@ -1577,8 +2084,20 @@
       <c r="H19" s="6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R19" s="19">
+        <v>46152</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="T19" s="19">
+        <v>46183</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -1603,8 +2122,20 @@
       <c r="H20" s="8" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R20" s="19">
+        <v>46153</v>
+      </c>
+      <c r="S20" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="T20" s="19">
+        <v>46184</v>
+      </c>
+      <c r="U20" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
@@ -1619,8 +2150,20 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="19">
+        <v>46154</v>
+      </c>
+      <c r="S21" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="T21" s="19">
+        <v>46185</v>
+      </c>
+      <c r="U21" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>105</v>
       </c>
@@ -1631,8 +2174,20 @@
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
-    </row>
-    <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R22" s="19">
+        <v>46155</v>
+      </c>
+      <c r="S22" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="T22" s="19">
+        <v>46186</v>
+      </c>
+      <c r="U22" s="10" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
         <v>0</v>
@@ -1655,8 +2210,20 @@
       <c r="H23" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R23" s="19">
+        <v>46156</v>
+      </c>
+      <c r="S23" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="T23" s="19">
+        <v>46187</v>
+      </c>
+      <c r="U23" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -1677,8 +2244,20 @@
       <c r="H24" s="8" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R24" s="19">
+        <v>46157</v>
+      </c>
+      <c r="S24" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="T24" s="19">
+        <v>46188</v>
+      </c>
+      <c r="U24" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
@@ -1703,8 +2282,20 @@
       <c r="H25" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R25" s="19">
+        <v>46158</v>
+      </c>
+      <c r="S25" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="T25" s="19">
+        <v>46189</v>
+      </c>
+      <c r="U25" s="10" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
@@ -1729,8 +2320,20 @@
       <c r="H26" s="8" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R26" s="19">
+        <v>46159</v>
+      </c>
+      <c r="S26" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="T26" s="19">
+        <v>46190</v>
+      </c>
+      <c r="U26" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -1745,8 +2348,20 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R27" s="19">
+        <v>46160</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="T27" s="19">
+        <v>46191</v>
+      </c>
+      <c r="U27" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
@@ -1759,11 +2374,119 @@
         <v>115</v>
       </c>
       <c r="H28" s="1"/>
-    </row>
-    <row r="37" spans="1:8" ht="122.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
-        <v>135</v>
-      </c>
+      <c r="R28" s="19">
+        <v>46161</v>
+      </c>
+      <c r="S28" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="T28" s="19">
+        <v>46192</v>
+      </c>
+      <c r="U28" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R29" s="19">
+        <v>46162</v>
+      </c>
+      <c r="S29" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="T29" s="19">
+        <v>46193</v>
+      </c>
+      <c r="U29" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="R30" s="19">
+        <v>46163</v>
+      </c>
+      <c r="S30" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="T30" s="19">
+        <v>46194</v>
+      </c>
+      <c r="U30" s="16"/>
+    </row>
+    <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="R31" s="19">
+        <v>46164</v>
+      </c>
+      <c r="S31" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="T31" s="19">
+        <v>46195</v>
+      </c>
+      <c r="U31" s="16"/>
+    </row>
+    <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="R32" s="19">
+        <v>46165</v>
+      </c>
+      <c r="S32" s="16" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="R33" s="19">
+        <v>46166</v>
+      </c>
+      <c r="S33" s="16"/>
+    </row>
+    <row r="34" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+    </row>
+    <row r="35" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -1772,8 +2495,78 @@
       <c r="G37" s="11"/>
       <c r="H37" s="11"/>
     </row>
+    <row r="38" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R43" s="19"/>
+    </row>
+    <row r="44" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R44" s="19"/>
+    </row>
+    <row r="45" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R45" s="19"/>
+    </row>
+    <row r="46" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R46" s="19"/>
+    </row>
+    <row r="47" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R47" s="19"/>
+    </row>
+    <row r="48" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R49" s="19"/>
+    </row>
+    <row r="50" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R50" s="19"/>
+    </row>
+    <row r="51" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R51" s="19"/>
+    </row>
+    <row r="52" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R52" s="19"/>
+    </row>
+    <row r="53" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R53" s="19"/>
+    </row>
+    <row r="54" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R54" s="19"/>
+    </row>
+    <row r="55" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R55" s="19"/>
+    </row>
+    <row r="56" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBADD7C9-D4F5-4BFD-A95E-17088E02D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709F09FD-E2D1-4B1D-AE05-2EA0B33B3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6972" yWindow="0" windowWidth="16164" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="202">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -831,6 +831,26 @@
   </si>
   <si>
     <t>计算机组成原理滚动复习计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统滚动复习计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>87、88、89</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90、91、92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93、94、95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>96、97、98、99、100、101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -933,7 +953,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -956,6 +976,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -963,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -995,15 +1059,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1013,16 +1092,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1306,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V78"/>
+  <dimension ref="A1:W78"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="15.77734375" style="2" customWidth="1"/>
@@ -1315,33 +1400,34 @@
     <col min="11" max="14" width="8.88671875" style="2"/>
     <col min="15" max="15" width="11" style="2" customWidth="1"/>
     <col min="16" max="17" width="8.88671875" style="2"/>
-    <col min="18" max="18" width="12.88671875" style="18" customWidth="1"/>
+    <col min="18" max="18" width="12.88671875" style="12" customWidth="1"/>
     <col min="19" max="19" width="49.6640625" style="10" customWidth="1"/>
     <col min="20" max="20" width="12.77734375" style="10" customWidth="1"/>
     <col min="21" max="21" width="49.6640625" style="10" customWidth="1"/>
     <col min="22" max="22" width="12.88671875" style="10" customWidth="1"/>
-    <col min="23" max="16384" width="8.88671875" style="2"/>
+    <col min="23" max="23" width="49.21875" style="10" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="J1" s="13" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
       <c r="R1" s="17" t="s">
         <v>195</v>
       </c>
@@ -1350,8 +1436,12 @@
         <v>196</v>
       </c>
       <c r="U1" s="17"/>
-    </row>
-    <row r="2" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="W1" s="17"/>
+    </row>
+    <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1392,23 +1482,26 @@
       <c r="O2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="R2" s="18" t="s">
+      <c r="R2" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="11" t="s">
         <v>137</v>
       </c>
       <c r="V2" s="10" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W2" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1447,20 +1540,20 @@
       <c r="O3" s="1">
         <v>315</v>
       </c>
-      <c r="R3" s="19">
-        <v>46136</v>
-      </c>
-      <c r="S3" s="10" t="s">
+      <c r="R3" s="15">
+        <v>46139</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="T3" s="19">
-        <v>46167</v>
-      </c>
-      <c r="U3" s="10" t="s">
+      <c r="T3" s="15">
+        <v>46170</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1473,10 +1566,10 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
@@ -1499,20 +1592,20 @@
       <c r="O4" s="1">
         <v>325</v>
       </c>
-      <c r="R4" s="19">
-        <v>46137</v>
-      </c>
-      <c r="S4" s="10" t="s">
+      <c r="R4" s="15">
+        <v>46140</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="19">
-        <v>46168</v>
-      </c>
-      <c r="U4" s="10" t="s">
+      <c r="T4" s="15">
+        <v>46171</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1534,7 +1627,7 @@
       <c r="G5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="1"/>
@@ -1543,20 +1636,20 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="R5" s="19">
-        <v>46138</v>
-      </c>
-      <c r="S5" s="10" t="s">
+      <c r="R5" s="15">
+        <v>46141</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="T5" s="19">
-        <v>46169</v>
-      </c>
-      <c r="U5" s="10" t="s">
+      <c r="T5" s="15">
+        <v>46172</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1569,17 +1662,17 @@
       <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>37</v>
+      <c r="E6" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1587,68 +1680,68 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="R6" s="19">
-        <v>46139</v>
-      </c>
-      <c r="S6" s="10" t="s">
+      <c r="R6" s="15">
+        <v>46142</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="T6" s="19">
-        <v>46170</v>
-      </c>
-      <c r="U6" s="10" t="s">
+      <c r="T6" s="15">
+        <v>46173</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="R7" s="19">
-        <v>46140</v>
-      </c>
-      <c r="S7" s="10" t="s">
+      <c r="R7" s="15">
+        <v>46143</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="T7" s="19">
-        <v>46171</v>
-      </c>
-      <c r="U7" s="10" t="s">
+      <c r="T7" s="15">
+        <v>46174</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1667,20 +1760,20 @@
       <c r="O8" s="1">
         <v>395</v>
       </c>
-      <c r="R8" s="19">
-        <v>46141</v>
-      </c>
-      <c r="S8" s="10" t="s">
+      <c r="R8" s="15">
+        <v>46144</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="T8" s="19">
-        <v>46172</v>
-      </c>
-      <c r="U8" s="10" t="s">
+      <c r="T8" s="15">
+        <v>46175</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>0</v>
@@ -1703,251 +1796,251 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="R9" s="19">
-        <v>46142</v>
-      </c>
-      <c r="S9" s="10" t="s">
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="R9" s="15">
+        <v>46145</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="T9" s="19">
-        <v>46173</v>
-      </c>
-      <c r="U9" s="10" t="s">
+      <c r="T9" s="15">
+        <v>46176</v>
+      </c>
+      <c r="U9" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>128</v>
       </c>
       <c r="K10" s="10"/>
-      <c r="R10" s="19">
-        <v>46143</v>
-      </c>
-      <c r="S10" s="10" t="s">
+      <c r="R10" s="15">
+        <v>46146</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="T10" s="19">
-        <v>46174</v>
-      </c>
-      <c r="U10" s="10" t="s">
+      <c r="T10" s="15">
+        <v>46177</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="4">
+      <c r="H11" s="4">
         <v>43</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="R11" s="19">
-        <v>46144</v>
-      </c>
-      <c r="S11" s="10" t="s">
+      <c r="R11" s="15">
+        <v>46147</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="T11" s="19">
-        <v>46175</v>
-      </c>
-      <c r="U11" s="10" t="s">
+      <c r="T11" s="15">
+        <v>46178</v>
+      </c>
+      <c r="U11" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="R12" s="19">
-        <v>46145</v>
-      </c>
-      <c r="S12" s="10" t="s">
+      <c r="R12" s="15">
+        <v>46148</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="T12" s="19">
-        <v>46176</v>
-      </c>
-      <c r="U12" s="10" t="s">
+      <c r="T12" s="15">
+        <v>46179</v>
+      </c>
+      <c r="U12" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="R13" s="19">
-        <v>46146</v>
-      </c>
-      <c r="S13" s="10" t="s">
+      <c r="R13" s="15">
+        <v>46149</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="T13" s="19">
-        <v>46177</v>
-      </c>
-      <c r="U13" s="10" t="s">
+      <c r="T13" s="15">
+        <v>46180</v>
+      </c>
+      <c r="U13" s="1" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="R14" s="19">
-        <v>46147</v>
-      </c>
-      <c r="S14" s="10" t="s">
+      <c r="R14" s="15">
+        <v>46150</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="T14" s="19">
-        <v>46178</v>
-      </c>
-      <c r="U14" s="10" t="s">
+      <c r="T14" s="15">
+        <v>46181</v>
+      </c>
+      <c r="U14" s="1" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+    <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="J15" s="16"/>
-      <c r="R15" s="19">
-        <v>46148</v>
-      </c>
-      <c r="S15" s="10" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
+      <c r="R15" s="15">
+        <v>46151</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="T15" s="19">
-        <v>46179</v>
-      </c>
-      <c r="U15" s="10" t="s">
+      <c r="T15" s="15">
+        <v>46182</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
         <v>0</v>
@@ -1970,16 +2063,16 @@
       <c r="H16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R16" s="19">
-        <v>46149</v>
-      </c>
-      <c r="S16" s="10" t="s">
+      <c r="R16" s="15">
+        <v>46152</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="T16" s="19">
-        <v>46180</v>
-      </c>
-      <c r="U16" s="10" t="s">
+      <c r="T16" s="15">
+        <v>46183</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>182</v>
       </c>
     </row>
@@ -1988,36 +2081,36 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="R17" s="19">
-        <v>46150</v>
-      </c>
-      <c r="S17" s="10" t="s">
+      <c r="R17" s="15">
+        <v>46153</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="T17" s="19">
-        <v>46181</v>
-      </c>
-      <c r="U17" s="10" t="s">
+      <c r="T17" s="15">
+        <v>46184</v>
+      </c>
+      <c r="U17" s="1" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2026,36 +2119,36 @@
         <v>8</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="R18" s="19">
-        <v>46151</v>
-      </c>
-      <c r="S18" s="10" t="s">
+      <c r="R18" s="15">
+        <v>46154</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="T18" s="19">
-        <v>46182</v>
-      </c>
-      <c r="U18" s="10" t="s">
+      <c r="T18" s="15">
+        <v>46185</v>
+      </c>
+      <c r="U18" s="1" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2064,36 +2157,36 @@
         <v>9</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="R19" s="19">
-        <v>46152</v>
-      </c>
-      <c r="S19" s="10" t="s">
+      <c r="R19" s="15">
+        <v>46155</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="T19" s="19">
-        <v>46183</v>
-      </c>
-      <c r="U19" s="10" t="s">
+      <c r="T19" s="15">
+        <v>46186</v>
+      </c>
+      <c r="U19" s="1" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2101,37 +2194,37 @@
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="H20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="R20" s="19">
-        <v>46153</v>
-      </c>
-      <c r="S20" s="10" t="s">
+      <c r="R20" s="15">
+        <v>46156</v>
+      </c>
+      <c r="S20" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T20" s="19">
-        <v>46184</v>
-      </c>
-      <c r="U20" s="10" t="s">
+      <c r="T20" s="15">
+        <v>46187</v>
+      </c>
+      <c r="U20" s="1" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2140,50 +2233,50 @@
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="R21" s="19">
-        <v>46154</v>
-      </c>
-      <c r="S21" s="10" t="s">
+      <c r="R21" s="15">
+        <v>46157</v>
+      </c>
+      <c r="S21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="T21" s="19">
-        <v>46185</v>
-      </c>
-      <c r="U21" s="10" t="s">
+      <c r="T21" s="15">
+        <v>46188</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="R22" s="19">
-        <v>46155</v>
-      </c>
-      <c r="S22" s="10" t="s">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="R22" s="15">
+        <v>46158</v>
+      </c>
+      <c r="S22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="T22" s="19">
-        <v>46186</v>
-      </c>
-      <c r="U22" s="10" t="s">
+      <c r="T22" s="15">
+        <v>46189</v>
+      </c>
+      <c r="U22" s="1" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2210,16 +2303,16 @@
       <c r="H23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R23" s="19">
-        <v>46156</v>
-      </c>
-      <c r="S23" s="10" t="s">
+      <c r="R23" s="15">
+        <v>46159</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="T23" s="19">
-        <v>46187</v>
-      </c>
-      <c r="U23" s="10" t="s">
+      <c r="T23" s="15">
+        <v>46190</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2230,30 +2323,30 @@
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="R24" s="19">
-        <v>46157</v>
-      </c>
-      <c r="S24" s="10" t="s">
+      <c r="R24" s="15">
+        <v>46160</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T24" s="19">
-        <v>46188</v>
-      </c>
-      <c r="U24" s="10" t="s">
+      <c r="T24" s="15">
+        <v>46191</v>
+      </c>
+      <c r="U24" s="1" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2262,36 +2355,36 @@
         <v>8</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="G25" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="R25" s="19">
-        <v>46158</v>
-      </c>
-      <c r="S25" s="10" t="s">
+      <c r="R25" s="15">
+        <v>46161</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="T25" s="19">
-        <v>46189</v>
-      </c>
-      <c r="U25" s="10" t="s">
+      <c r="T25" s="15">
+        <v>46192</v>
+      </c>
+      <c r="U25" s="1" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2300,36 +2393,36 @@
         <v>9</v>
       </c>
       <c r="B26" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="G26" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E26" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="R26" s="19">
-        <v>46159</v>
-      </c>
-      <c r="S26" s="10" t="s">
+      <c r="R26" s="15">
+        <v>46162</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="T26" s="19">
-        <v>46190</v>
-      </c>
-      <c r="U26" s="10" t="s">
+      <c r="T26" s="15">
+        <v>46193</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2338,26 +2431,34 @@
         <v>10</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="G27" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="R27" s="19">
-        <v>46160</v>
-      </c>
-      <c r="S27" s="10" t="s">
+      <c r="R27" s="15">
+        <v>46163</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="T27" s="19">
-        <v>46191</v>
-      </c>
-      <c r="U27" s="10" t="s">
+      <c r="T27" s="15">
+        <v>46194</v>
+      </c>
+      <c r="U27" s="1" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2369,173 +2470,175 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1" t="s">
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H28" s="1"/>
-      <c r="R28" s="19">
-        <v>46161</v>
-      </c>
-      <c r="S28" s="10" t="s">
+      <c r="R28" s="15">
+        <v>46164</v>
+      </c>
+      <c r="S28" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="T28" s="19">
-        <v>46192</v>
-      </c>
-      <c r="U28" s="10" t="s">
+      <c r="T28" s="15">
+        <v>46195</v>
+      </c>
+      <c r="U28" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R29" s="19">
-        <v>46162</v>
-      </c>
-      <c r="S29" s="10" t="s">
+      <c r="R29" s="15">
+        <v>46165</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T29" s="19">
-        <v>46193</v>
-      </c>
-      <c r="U29" s="16" t="s">
+      <c r="T29" s="15">
+        <v>46196</v>
+      </c>
+      <c r="U29" s="19" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="R30" s="19">
-        <v>46163</v>
-      </c>
-      <c r="S30" s="10" t="s">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="R30" s="15">
+        <v>46166</v>
+      </c>
+      <c r="S30" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="T30" s="19">
-        <v>46194</v>
-      </c>
-      <c r="U30" s="16"/>
+      <c r="T30" s="15">
+        <v>46197</v>
+      </c>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="R31" s="19">
-        <v>46164</v>
-      </c>
-      <c r="S31" s="10" t="s">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="R31" s="15">
+        <v>46167</v>
+      </c>
+      <c r="S31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="T31" s="19">
-        <v>46195</v>
-      </c>
-      <c r="U31" s="16"/>
+      <c r="T31" s="15">
+        <v>46198</v>
+      </c>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="R32" s="19">
-        <v>46165</v>
-      </c>
-      <c r="S32" s="16" t="s">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="R32" s="15">
+        <v>46168</v>
+      </c>
+      <c r="S32" s="19" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="R33" s="19">
-        <v>46166</v>
-      </c>
-      <c r="S33" s="16"/>
-    </row>
-    <row r="34" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-    </row>
-    <row r="38" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R43" s="19"/>
-    </row>
-    <row r="44" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R44" s="19"/>
-    </row>
-    <row r="45" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R45" s="19"/>
-    </row>
-    <row r="46" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R46" s="19"/>
-    </row>
-    <row r="47" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R47" s="19"/>
-    </row>
-    <row r="48" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="23"/>
+    </row>
+    <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="R33" s="15">
+        <v>46169</v>
+      </c>
+      <c r="S33" s="19"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="25"/>
+    </row>
+    <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" s="16"/>
+    </row>
+    <row r="38" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="R43" s="13"/>
+    </row>
+    <row r="44" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R44" s="13"/>
+    </row>
+    <row r="45" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R45" s="13"/>
+    </row>
+    <row r="46" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R46" s="13"/>
+    </row>
+    <row r="47" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R47" s="13"/>
+    </row>
+    <row r="48" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R49" s="19"/>
+      <c r="R49" s="13"/>
     </row>
     <row r="50" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R50" s="19"/>
+      <c r="R50" s="13"/>
     </row>
     <row r="51" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R51" s="19"/>
+      <c r="R51" s="13"/>
     </row>
     <row r="52" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R52" s="19"/>
+      <c r="R52" s="13"/>
     </row>
     <row r="53" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R53" s="19"/>
+      <c r="R53" s="13"/>
     </row>
     <row r="54" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R54" s="19"/>
+      <c r="R54" s="13"/>
     </row>
     <row r="55" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R55" s="19"/>
+      <c r="R55" s="13"/>
     </row>
     <row r="56" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2561,13 +2664,13 @@
     <row r="77" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="R1:S1"/>
+  <mergeCells count="15">
     <mergeCell ref="A30:H34"/>
     <mergeCell ref="S32:S33"/>
     <mergeCell ref="U29:U31"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="T32:U33"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
     <mergeCell ref="J9:O9"/>
@@ -2576,6 +2679,7 @@
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
+    <mergeCell ref="R1:S1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709F09FD-E2D1-4B1D-AE05-2EA0B33B3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6972" yWindow="0" windowWidth="16164" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6492" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1027,7 +1027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1077,19 +1077,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1104,10 +1098,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1410,36 +1407,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="J1" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="R1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1566,10 +1563,10 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
@@ -1732,16 +1729,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1796,14 +1793,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="15">
         <v>46145</v>
       </c>
@@ -1999,7 +1996,7 @@
       <c r="H14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="26" t="s">
         <v>135</v>
       </c>
       <c r="R14" s="15">
@@ -2016,17 +2013,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="26"/>
       <c r="R15" s="15">
         <v>46151</v>
       </c>
@@ -2257,16 +2254,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="R22" s="15">
         <v>46158</v>
       </c>
@@ -2498,21 +2495,21 @@
       <c r="T29" s="15">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="18" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="15">
         <v>46166</v>
       </c>
@@ -2522,17 +2519,17 @@
       <c r="T30" s="15">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="15">
         <v>46167</v>
       </c>
@@ -2542,51 +2539,51 @@
       <c r="T31" s="15">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="15">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="T32" s="22"/>
-      <c r="U32" s="23"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="15">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="24"/>
-      <c r="U33" s="25"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2599,11 +2596,11 @@
     <row r="41" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
       <c r="R43" s="13"/>
     </row>
     <row r="44" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2665,11 +2662,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2680,6 +2672,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709F09FD-E2D1-4B1D-AE05-2EA0B33B3921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFF5A56-2AFA-49A5-BA4A-8D94E48177EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6492" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5076" yWindow="720" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1077,13 +1077,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1096,15 +1105,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1407,36 +1407,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1563,10 +1563,10 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
@@ -1650,13 +1650,13 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1729,16 +1729,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1793,14 +1793,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="15">
         <v>46145</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="H14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="21" t="s">
         <v>135</v>
       </c>
       <c r="R14" s="15">
@@ -2013,17 +2013,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="15">
         <v>46151</v>
       </c>
@@ -2254,16 +2254,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="15">
         <v>46158</v>
       </c>
@@ -2495,21 +2495,21 @@
       <c r="T29" s="15">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="19" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="15">
         <v>46166</v>
       </c>
@@ -2519,17 +2519,17 @@
       <c r="T30" s="15">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="15">
         <v>46167</v>
       </c>
@@ -2539,51 +2539,51 @@
       <c r="T31" s="15">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="15">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="15">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2662,6 +2662,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2672,11 +2677,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFF5A56-2AFA-49A5-BA4A-8D94E48177EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8868A953-0C89-4D77-8DB1-F25B01D73323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5076" yWindow="720" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="204">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -851,6 +851,14 @@
   </si>
   <si>
     <t>96、97、98、99、100、101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月开始，每月两篇小作文模板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到9月份全部背完</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1659,7 +1667,7 @@
       <c r="D6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>198</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -2059,6 +2067,12 @@
       </c>
       <c r="H16" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="R16" s="15">
         <v>46152</v>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8868A953-0C89-4D77-8DB1-F25B01D73323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00FDC2E-4E53-4B59-9EAA-76FA3ED8450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1085,22 +1085,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1113,6 +1104,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1415,36 +1415,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="J1" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="R1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1571,10 +1571,10 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
@@ -1670,7 +1670,7 @@
       <c r="E6" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="5" t="s">
         <v>199</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1737,16 +1737,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1801,14 +1801,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="15">
         <v>46145</v>
       </c>
@@ -2004,7 +2004,7 @@
       <c r="H14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="26" t="s">
         <v>135</v>
       </c>
       <c r="R14" s="15">
@@ -2021,17 +2021,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="26"/>
       <c r="R15" s="15">
         <v>46151</v>
       </c>
@@ -2268,16 +2268,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="R22" s="15">
         <v>46158</v>
       </c>
@@ -2509,21 +2509,21 @@
       <c r="T29" s="15">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="18" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="15">
         <v>46166</v>
       </c>
@@ -2533,17 +2533,17 @@
       <c r="T30" s="15">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="15">
         <v>46167</v>
       </c>
@@ -2553,51 +2553,51 @@
       <c r="T31" s="15">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="15">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="15">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2676,11 +2676,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2691,6 +2686,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00FDC2E-4E53-4B59-9EAA-76FA3ED8450C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C88F47-10F8-4F7F-86AA-2489B8B6175D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1085,13 +1085,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1104,15 +1113,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1415,36 +1415,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1571,10 +1571,10 @@
       <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="F6" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="5" t="s">
         <v>200</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -1737,16 +1737,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1801,14 +1801,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="15">
         <v>46145</v>
       </c>
@@ -2004,7 +2004,7 @@
       <c r="H14" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="21" t="s">
         <v>135</v>
       </c>
       <c r="R14" s="15">
@@ -2021,17 +2021,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="15">
         <v>46151</v>
       </c>
@@ -2268,16 +2268,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="15">
         <v>46158</v>
       </c>
@@ -2509,21 +2509,21 @@
       <c r="T29" s="15">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="19" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="15">
         <v>46166</v>
       </c>
@@ -2533,17 +2533,17 @@
       <c r="T30" s="15">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="15">
         <v>46167</v>
       </c>
@@ -2553,51 +2553,51 @@
       <c r="T31" s="15">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="15">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="15">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2676,6 +2676,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2686,11 +2691,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C88F47-10F8-4F7F-86AA-2489B8B6175D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7662B452-D235-44FD-B472-42AE190266D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3444" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1035,16 +1035,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1085,22 +1082,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1113,6 +1101,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1405,46 +1402,46 @@
     <col min="11" max="14" width="8.88671875" style="2"/>
     <col min="15" max="15" width="11" style="2" customWidth="1"/>
     <col min="16" max="17" width="8.88671875" style="2"/>
-    <col min="18" max="18" width="12.88671875" style="12" customWidth="1"/>
-    <col min="19" max="19" width="49.6640625" style="10" customWidth="1"/>
-    <col min="20" max="20" width="12.77734375" style="10" customWidth="1"/>
-    <col min="21" max="21" width="49.6640625" style="10" customWidth="1"/>
-    <col min="22" max="22" width="12.88671875" style="10" customWidth="1"/>
-    <col min="23" max="23" width="49.21875" style="10" customWidth="1"/>
+    <col min="18" max="18" width="12.88671875" style="11" customWidth="1"/>
+    <col min="19" max="19" width="49.6640625" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.77734375" style="9" customWidth="1"/>
+    <col min="21" max="21" width="49.6640625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="12.88671875" style="9" customWidth="1"/>
+    <col min="23" max="23" width="49.21875" style="9" customWidth="1"/>
     <col min="24" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="J1" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="R1" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="18"/>
+      <c r="T1" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="18"/>
+      <c r="V1" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="18"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1487,22 +1484,22 @@
       <c r="O2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="R2" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="S2" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V2" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="W2" s="9" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1510,23 +1507,23 @@
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1545,13 +1542,13 @@
       <c r="O3" s="1">
         <v>315</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="14">
         <v>46139</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="14">
         <v>46170</v>
       </c>
       <c r="U3" s="1" t="s">
@@ -1562,23 +1559,23 @@
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="24"/>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1597,13 +1594,13 @@
       <c r="O4" s="1">
         <v>325</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="14">
         <v>46140</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="T4" s="15">
+      <c r="T4" s="14">
         <v>46171</v>
       </c>
       <c r="U4" s="1" t="s">
@@ -1614,25 +1611,25 @@
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="1"/>
@@ -1641,13 +1638,13 @@
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="R5" s="15">
+      <c r="R5" s="14">
         <v>46141</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="T5" s="15">
+      <c r="T5" s="14">
         <v>46172</v>
       </c>
       <c r="U5" s="1" t="s">
@@ -1658,25 +1655,25 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>201</v>
       </c>
       <c r="J6" s="1"/>
@@ -1685,13 +1682,13 @@
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="R6" s="15">
+      <c r="R6" s="14">
         <v>46142</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <v>46173</v>
       </c>
       <c r="U6" s="1" t="s">
@@ -1705,13 +1702,13 @@
       <c r="B7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="1"/>
@@ -1723,13 +1720,13 @@
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="R7" s="15">
+      <c r="R7" s="14">
         <v>46143</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="14">
         <v>46174</v>
       </c>
       <c r="U7" s="1" t="s">
@@ -1737,16 +1734,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1765,13 +1762,13 @@
       <c r="O8" s="1">
         <v>395</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="14">
         <v>46144</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="14">
         <v>46175</v>
       </c>
       <c r="U8" s="1" t="s">
@@ -1801,21 +1798,21 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="R9" s="15">
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="R9" s="14">
         <v>46145</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="14">
         <v>46176</v>
       </c>
       <c r="U9" s="1" t="s">
@@ -1826,30 +1823,30 @@
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="4" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="K10" s="10"/>
-      <c r="R10" s="15">
+      <c r="K10" s="9"/>
+      <c r="R10" s="14">
         <v>46146</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="T10" s="15">
+      <c r="T10" s="14">
         <v>46177</v>
       </c>
       <c r="U10" s="1" t="s">
@@ -1860,37 +1857,37 @@
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="3">
         <v>43</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="14">
         <v>46147</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="14">
         <v>46178</v>
       </c>
       <c r="U11" s="1" t="s">
@@ -1901,37 +1898,37 @@
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="14">
         <v>46148</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="14">
         <v>46179</v>
       </c>
       <c r="U12" s="1" t="s">
@@ -1942,37 +1939,37 @@
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="14">
         <v>46149</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="14">
         <v>46180</v>
       </c>
       <c r="U13" s="1" t="s">
@@ -1983,37 +1980,37 @@
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>62</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="14">
         <v>46150</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="14">
         <v>46181</v>
       </c>
       <c r="U14" s="1" t="s">
@@ -2021,24 +2018,24 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
-      <c r="R15" s="15">
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="J15" s="25"/>
+      <c r="R15" s="14">
         <v>46151</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="14">
         <v>46182</v>
       </c>
       <c r="U15" s="1" t="s">
@@ -2068,19 +2065,19 @@
       <c r="H16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="R16" s="15">
+      <c r="R16" s="14">
         <v>46152</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="14">
         <v>46183</v>
       </c>
       <c r="U16" s="1" t="s">
@@ -2091,34 +2088,34 @@
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="14">
         <v>46153</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="14">
         <v>46184</v>
       </c>
       <c r="U17" s="1" t="s">
@@ -2129,34 +2126,34 @@
       <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="R18" s="15">
+      <c r="R18" s="14">
         <v>46154</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="14">
         <v>46185</v>
       </c>
       <c r="U18" s="1" t="s">
@@ -2167,34 +2164,34 @@
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="R19" s="15">
+      <c r="R19" s="14">
         <v>46155</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="14">
         <v>46186</v>
       </c>
       <c r="U19" s="1" t="s">
@@ -2205,34 +2202,34 @@
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>88</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="R20" s="15">
+      <c r="R20" s="14">
         <v>46156</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="T20" s="15">
+      <c r="T20" s="14">
         <v>46187</v>
       </c>
       <c r="U20" s="1" t="s">
@@ -2243,24 +2240,24 @@
       <c r="A21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="R21" s="15">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="R21" s="14">
         <v>46157</v>
       </c>
       <c r="S21" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="T21" s="15">
+      <c r="T21" s="14">
         <v>46188</v>
       </c>
       <c r="U21" s="1" t="s">
@@ -2268,23 +2265,23 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="R22" s="15">
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="R22" s="14">
         <v>46158</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="T22" s="15">
+      <c r="T22" s="14">
         <v>46189</v>
       </c>
       <c r="U22" s="1" t="s">
@@ -2314,13 +2311,13 @@
       <c r="H23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R23" s="15">
+      <c r="R23" s="14">
         <v>46159</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="14">
         <v>46190</v>
       </c>
       <c r="U23" s="1" t="s">
@@ -2331,30 +2328,30 @@
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="R24" s="15">
+      <c r="R24" s="14">
         <v>46160</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="T24" s="15">
+      <c r="T24" s="14">
         <v>46191</v>
       </c>
       <c r="U24" s="1" t="s">
@@ -2365,34 +2362,34 @@
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="R25" s="15">
+      <c r="R25" s="14">
         <v>46161</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="T25" s="15">
+      <c r="T25" s="14">
         <v>46192</v>
       </c>
       <c r="U25" s="1" t="s">
@@ -2403,34 +2400,34 @@
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="R26" s="15">
+      <c r="R26" s="14">
         <v>46162</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="T26" s="15">
+      <c r="T26" s="14">
         <v>46193</v>
       </c>
       <c r="U26" s="1" t="s">
@@ -2441,32 +2438,32 @@
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="7" t="s">
         <v>98</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="R27" s="15">
+      <c r="R27" s="14">
         <v>46163</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="T27" s="15">
+      <c r="T27" s="14">
         <v>46194</v>
       </c>
       <c r="U27" s="1" t="s">
@@ -2481,18 +2478,18 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
       <c r="H28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="R28" s="15">
+      <c r="R28" s="14">
         <v>46164</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="T28" s="15">
+      <c r="T28" s="14">
         <v>46195</v>
       </c>
       <c r="U28" s="1" t="s">
@@ -2500,109 +2497,109 @@
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R29" s="15">
+      <c r="R29" s="14">
         <v>46165</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="T29" s="15">
+      <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="17" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="R30" s="15">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="R30" s="14">
         <v>46166</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="T30" s="15">
+      <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="17"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="R31" s="15">
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="R31" s="14">
         <v>46167</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="T31" s="15">
+      <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="17"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="R32" s="15">
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="19"/>
+      <c r="U32" s="20"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="R33" s="15">
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="21"/>
+      <c r="U33" s="22"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H37" s="16"/>
+      <c r="H37" s="15"/>
     </row>
     <row r="38" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2610,46 +2607,46 @@
     <row r="41" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="R43" s="13"/>
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="R43" s="12"/>
     </row>
     <row r="44" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R44" s="13"/>
+      <c r="R44" s="12"/>
     </row>
     <row r="45" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R45" s="13"/>
+      <c r="R45" s="12"/>
     </row>
     <row r="46" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R46" s="13"/>
+      <c r="R46" s="12"/>
     </row>
     <row r="47" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R47" s="13"/>
+      <c r="R47" s="12"/>
     </row>
     <row r="48" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R49" s="13"/>
+      <c r="R49" s="12"/>
     </row>
     <row r="50" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R50" s="13"/>
+      <c r="R50" s="12"/>
     </row>
     <row r="51" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R51" s="13"/>
+      <c r="R51" s="12"/>
     </row>
     <row r="52" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R52" s="13"/>
+      <c r="R52" s="12"/>
     </row>
     <row r="53" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R53" s="13"/>
+      <c r="R53" s="12"/>
     </row>
     <row r="54" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R54" s="13"/>
+      <c r="R54" s="12"/>
     </row>
     <row r="55" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="R55" s="13"/>
+      <c r="R55" s="12"/>
     </row>
     <row r="56" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="18:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2676,11 +2673,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2691,6 +2683,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7662B452-D235-44FD-B472-42AE190266D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F82F0C9-919D-4A60-836D-51F157BFBE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3444" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="205">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -859,6 +859,10 @@
   </si>
   <si>
     <t>到9月份全部背完</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据结构提前一天完结！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1082,13 +1086,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1101,15 +1114,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1412,36 +1416,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="J1" s="18" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="J1" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="R1" s="18" t="s">
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="R1" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18" t="s">
+      <c r="S1" s="16"/>
+      <c r="T1" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18" t="s">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="W1" s="18"/>
+      <c r="W1" s="16"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1568,10 +1572,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="24"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1700,7 +1704,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>204</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>35</v>
@@ -1734,16 +1738,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
       <c r="J8" s="1" t="s">
         <v>132</v>
       </c>
@@ -1798,14 +1802,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2001,7 +2005,7 @@
       <c r="H14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="20" t="s">
         <v>135</v>
       </c>
       <c r="R14" s="14">
@@ -2018,17 +2022,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="J15" s="25"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="J15" s="20"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2265,16 +2269,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2506,21 +2510,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="17" t="s">
+      <c r="U29" s="18" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2530,17 +2534,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="17"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2550,51 +2554,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="17"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="17" t="s">
+      <c r="S32" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="T32" s="19"/>
-      <c r="U32" s="20"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="23"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="17"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="22"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="25"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2673,6 +2677,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2683,11 +2692,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F82F0C9-919D-4A60-836D-51F157BFBE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425A71F0-F141-4D90-B6CE-09BB80F34812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -169,10 +169,6 @@
   </si>
   <si>
     <t>02、03、04、05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>03、07、08、09</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -863,6 +859,10 @@
   </si>
   <si>
     <t>数据结构提前一天完结！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06、07、08、09</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -921,7 +921,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -961,6 +961,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1039,7 +1045,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1085,6 +1091,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1416,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="J1" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="R1" s="16" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="W1" s="16"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1471,40 +1480,40 @@
         <v>6</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="N2" s="1">
         <v>408</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R2" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="S2" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="S2" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="T2" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="U2" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="U2" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="V2" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="W2" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="W2" s="9" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1513,7 +1522,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>15</v>
@@ -1531,17 +1540,17 @@
         <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O3" s="1">
         <v>315</v>
@@ -1549,14 +1558,14 @@
       <c r="R3" s="14">
         <v>46139</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>139</v>
+      <c r="S3" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="T3" s="14">
         <v>46170</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1572,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="19"/>
+      <c r="E4" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1583,17 +1592,17 @@
         <v>24</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O4" s="1">
         <v>325</v>
@@ -1602,13 +1611,13 @@
         <v>46140</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T4" s="14">
         <v>46171</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1646,13 +1655,13 @@
         <v>46141</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T5" s="14">
         <v>46172</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1666,19 +1675,19 @@
         <v>33</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1690,30 +1699,30 @@
         <v>46142</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T6" s="14">
         <v>46173</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1728,28 +1737,28 @@
         <v>46143</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T7" s="14">
         <v>46174</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K8" s="1">
         <v>75</v>
@@ -1758,10 +1767,10 @@
         <v>70</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="O8" s="1">
         <v>395</v>
@@ -1770,13 +1779,13 @@
         <v>46144</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T8" s="14">
         <v>46175</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1802,25 +1811,25 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="J9" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T9" s="14">
         <v>46176</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1832,29 +1841,29 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K10" s="9"/>
       <c r="R10" s="14">
         <v>46146</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T10" s="14">
         <v>46177</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1862,40 +1871,40 @@
         <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H11" s="3">
         <v>43</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R11" s="14">
         <v>46147</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T11" s="14">
         <v>46178</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1903,40 +1912,40 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J12" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R12" s="14">
         <v>46148</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="T12" s="14">
         <v>46179</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1944,40 +1953,40 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R13" s="14">
         <v>46149</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T13" s="14">
         <v>46180</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1985,65 +1994,65 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="20" t="s">
-        <v>135</v>
+      <c r="J14" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="R14" s="14">
         <v>46150</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T14" s="14">
         <v>46181</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="J15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T15" s="14">
         <v>46182</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2070,22 +2079,22 @@
         <v>6</v>
       </c>
       <c r="J16" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="R16" s="14">
         <v>46152</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T16" s="14">
         <v>46183</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2093,37 +2102,37 @@
         <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="R17" s="14">
         <v>46153</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T17" s="14">
         <v>46184</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2134,34 +2143,34 @@
         <v>15</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="R18" s="14">
         <v>46154</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T18" s="14">
         <v>46185</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2169,37 +2178,37 @@
         <v>9</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="R19" s="14">
         <v>46155</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T19" s="14">
         <v>46186</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -2207,37 +2216,37 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G20" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="R20" s="14">
         <v>46156</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T20" s="14">
         <v>46187</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2245,10 +2254,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2259,37 +2268,37 @@
         <v>46157</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T21" s="14">
         <v>46188</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+      <c r="A22" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T22" s="14">
         <v>46189</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2319,13 +2328,13 @@
         <v>46159</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T23" s="14">
         <v>46190</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2335,31 +2344,31 @@
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="7" t="s">
+      <c r="G24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="R24" s="14">
         <v>46160</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T24" s="14">
         <v>46191</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2367,37 +2376,37 @@
         <v>8</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R25" s="14">
         <v>46161</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T25" s="14">
         <v>46192</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2405,37 +2414,37 @@
         <v>9</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="G26" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="H26" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>110</v>
       </c>
       <c r="R26" s="14">
         <v>46162</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="T26" s="14">
         <v>46193</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2443,35 +2452,35 @@
         <v>10</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E27" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>114</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H27" s="1"/>
       <c r="R27" s="14">
         <v>46163</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T27" s="14">
         <v>46194</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2485,19 +2494,19 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R28" s="14">
         <v>46164</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T28" s="14">
         <v>46195</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2505,100 +2514,100 @@
         <v>46165</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
-        <v>169</v>
+      <c r="U29" s="19" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="A30" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="T32" s="22"/>
-      <c r="U32" s="23"/>
+      <c r="S32" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="24"/>
-      <c r="U33" s="25"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -1095,22 +1095,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1123,6 +1114,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="J1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="R1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="26" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="26"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="18" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,11 +2686,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2701,6 +2696,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425A71F0-F141-4D90-B6CE-09BB80F34812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B350BB4D-BE5A-4699-8960-3806B6E959CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,13 +1095,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1114,15 +1123,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="D7" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="1"/>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="21" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="19" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,6 +2686,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2696,11 +2701,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B350BB4D-BE5A-4699-8960-3806B6E959CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753616CA-6A22-4A62-9D51-E2629BEF4954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1095,22 +1095,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1123,6 +1114,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="J1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="R1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -1840,7 +1840,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="16" t="s">
         <v>37</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="26" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="26"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="18" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,11 +2686,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2701,6 +2696,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753616CA-6A22-4A62-9D51-E2629BEF4954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DB822C-0A16-4DE5-B8A9-772AC34BCA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,13 +1095,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1114,15 +1123,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -1843,10 +1843,10 @@
       <c r="F10" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="16" t="s">
         <v>39</v>
       </c>
       <c r="J10" s="9" t="s">
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="21" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="19" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,6 +2686,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2696,11 +2701,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DB822C-0A16-4DE5-B8A9-772AC34BCA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BE80C7-D3C4-4E95-8031-307A60B0ACE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,22 +1095,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1123,6 +1114,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="J1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="R1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -1870,7 +1870,7 @@
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="16" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="26" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="26"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="18" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,11 +2686,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2701,6 +2696,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BE80C7-D3C4-4E95-8031-307A60B0ACE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3898A9C6-9B7A-4F8A-A4F6-3131069EC50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1095,13 +1095,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1114,15 +1123,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -1873,7 +1873,7 @@
       <c r="B11" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="16" t="s">
         <v>41</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="21" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="19" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,6 +2686,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2696,11 +2701,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3898A9C6-9B7A-4F8A-A4F6-3131069EC50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2B096C-85C2-4F61-83CA-9F4D0A3A40EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1610,7 +1610,7 @@
       <c r="R4" s="14">
         <v>46140</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="S4" s="4" t="s">
         <v>139</v>
       </c>
       <c r="T4" s="14">
@@ -1654,7 +1654,7 @@
       <c r="R5" s="14">
         <v>46141</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="4" t="s">
         <v>140</v>
       </c>
       <c r="T5" s="14">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2B096C-85C2-4F61-83CA-9F4D0A3A40EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36732D0-CE82-4545-B467-D592ABB0AD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,13 +1095,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1114,15 +1123,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="25"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1698,7 +1698,7 @@
       <c r="R6" s="14">
         <v>46142</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="4" t="s">
         <v>141</v>
       </c>
       <c r="T6" s="14">
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="26" t="s">
+      <c r="J14" s="21" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
+      <c r="U29" s="19" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
+      <c r="S32" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,6 +2686,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2696,11 +2701,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36732D0-CE82-4545-B467-D592ABB0AD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9928DEC1-E6B3-4BE9-94E3-3EDDD04632A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,22 +1095,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1123,6 +1114,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1425,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="J1" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="R1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="19"/>
+      <c r="T1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="19"/>
+      <c r="V1" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1581,10 +1581,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="25"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1747,16 +1747,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
       <c r="J8" s="1" t="s">
         <v>131</v>
       </c>
@@ -1811,14 +1811,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="H14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="26" t="s">
         <v>134</v>
       </c>
       <c r="R14" s="14">
@@ -2031,17 +2031,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="26"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2278,16 +2278,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2519,21 +2519,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="18" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2543,17 +2543,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="18"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2563,51 +2563,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="18"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="21"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="23"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,11 +2686,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2701,6 +2696,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9928DEC1-E6B3-4BE9-94E3-3EDDD04632A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D6BDE6-8CD6-4232-AAE3-495C16458F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="206">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -193,14 +193,6 @@
   </si>
   <si>
     <t>26、27、28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>29、30、31、32、33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>34、35、36、37</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -863,6 +855,18 @@
   </si>
   <si>
     <t>06、07、08、09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37、38、39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29、30、31、32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33、34、35、36</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1095,13 +1099,22 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1114,15 +1127,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1425,36 +1429,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="J1" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="R1" s="19" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="J1" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="R1" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="W1" s="19"/>
+      <c r="W1" s="17"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1480,40 +1484,40 @@
         <v>6</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N2" s="1">
         <v>408</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="V2" s="9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W2" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1522,7 +1526,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>15</v>
@@ -1540,17 +1544,17 @@
         <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="O3" s="1">
         <v>315</v>
@@ -1559,13 +1563,13 @@
         <v>46139</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="T3" s="14">
         <v>46170</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1581,10 +1585,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="25"/>
+      <c r="E4" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="20"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1592,17 +1596,17 @@
         <v>24</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O4" s="1">
         <v>325</v>
@@ -1611,13 +1615,13 @@
         <v>46140</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="T4" s="14">
         <v>46171</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1655,13 +1659,13 @@
         <v>46141</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T5" s="14">
         <v>46172</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1675,19 +1679,19 @@
         <v>33</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>198</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1699,13 +1703,13 @@
         <v>46142</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T6" s="14">
         <v>46173</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1713,13 +1717,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>36</v>
@@ -1737,28 +1741,28 @@
         <v>46143</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T7" s="14">
         <v>46174</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
       <c r="J8" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K8" s="1">
         <v>75</v>
@@ -1767,10 +1771,10 @@
         <v>70</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O8" s="1">
         <v>395</v>
@@ -1779,13 +1783,13 @@
         <v>46144</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="T8" s="14">
         <v>46175</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1811,25 +1815,25 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="J9" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="T9" s="14">
         <v>46176</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1850,20 +1854,20 @@
         <v>39</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K10" s="9"/>
       <c r="R10" s="14">
         <v>46146</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="T10" s="14">
         <v>46177</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1876,35 +1880,35 @@
       <c r="C11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="H11" s="3">
         <v>43</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R11" s="14">
         <v>46147</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="T11" s="14">
         <v>46178</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1912,40 +1916,40 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J12" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R12" s="14">
         <v>46148</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="T12" s="14">
         <v>46179</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1953,40 +1957,40 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R13" s="14">
         <v>46149</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="T13" s="14">
         <v>46180</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1994,65 +1998,65 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="26" t="s">
-        <v>134</v>
+      <c r="J14" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="R14" s="14">
         <v>46150</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="T14" s="14">
         <v>46181</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="J15" s="21"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="T15" s="14">
         <v>46182</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2079,22 +2083,22 @@
         <v>6</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R16" s="14">
         <v>46152</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="T16" s="14">
         <v>46183</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2102,37 +2106,37 @@
         <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="R17" s="14">
         <v>46153</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="T17" s="14">
         <v>46184</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2143,34 +2147,34 @@
         <v>15</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="R18" s="14">
         <v>46154</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="T18" s="14">
         <v>46185</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2178,37 +2182,37 @@
         <v>9</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="R19" s="14">
         <v>46155</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T19" s="14">
         <v>46186</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -2216,37 +2220,37 @@
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="R20" s="14">
         <v>46156</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="T20" s="14">
         <v>46187</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2254,10 +2258,10 @@
         <v>11</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2268,37 +2272,37 @@
         <v>46157</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="T21" s="14">
         <v>46188</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
+      <c r="A22" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="T22" s="14">
         <v>46189</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2328,13 +2332,13 @@
         <v>46159</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T23" s="14">
         <v>46190</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2344,31 +2348,31 @@
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="7" t="s">
+      <c r="H24" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>97</v>
       </c>
       <c r="R24" s="14">
         <v>46160</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T24" s="14">
         <v>46191</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2376,37 +2380,37 @@
         <v>8</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="H25" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="R25" s="14">
         <v>46161</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T25" s="14">
         <v>46192</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2414,37 +2418,37 @@
         <v>9</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="7" t="s">
+      <c r="H26" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="R26" s="14">
         <v>46162</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T26" s="14">
         <v>46193</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2452,35 +2456,35 @@
         <v>10</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="E27" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H27" s="1"/>
       <c r="R27" s="14">
         <v>46163</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="T27" s="14">
         <v>46194</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2494,19 +2498,19 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R28" s="14">
         <v>46164</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="T28" s="14">
         <v>46195</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2514,100 +2518,100 @@
         <v>46165</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="18" t="s">
-        <v>168</v>
+      <c r="U29" s="19" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
+      <c r="A30" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="18"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="18"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="T32" s="20"/>
-      <c r="U32" s="21"/>
+      <c r="S32" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="T32" s="23"/>
+      <c r="U32" s="24"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="18"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="23"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2686,6 +2690,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2696,11 +2705,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D6BDE6-8CD6-4232-AAE3-495C16458F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61791D8C-AF6A-404A-958E-E41A9DF9E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -925,7 +925,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -971,6 +971,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1049,7 +1055,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1127,6 +1133,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1953,7 +1962,7 @@
       </c>
     </row>
     <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61791D8C-AF6A-404A-958E-E41A9DF9E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D967F6C-BC49-4A89-87DB-CCBC1989327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="108" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1105,22 +1105,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1135,7 +1129,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1438,36 +1438,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="J1" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="R1" s="17" t="s">
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="R1" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17" t="s">
+      <c r="S1" s="20"/>
+      <c r="T1" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="U1" s="20"/>
+      <c r="V1" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="20"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1594,10 +1594,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="20"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1749,7 +1749,7 @@
       <c r="R7" s="14">
         <v>46143</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" s="4" t="s">
         <v>141</v>
       </c>
       <c r="T7" s="14">
@@ -1760,16 +1760,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
       <c r="J8" s="1" t="s">
         <v>129</v>
       </c>
@@ -1898,10 +1898,10 @@
       <c r="F11" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="16">
         <v>43</v>
       </c>
       <c r="J11" s="9" t="s">
@@ -1924,7 +1924,7 @@
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="16" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1962,7 +1962,7 @@
       </c>
     </row>
     <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2027,7 +2027,7 @@
       <c r="H14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="27" t="s">
         <v>132</v>
       </c>
       <c r="R14" s="14">
@@ -2044,17 +2044,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="J15" s="27"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2291,16 +2291,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2537,7 +2537,7 @@
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="18" t="s">
         <v>135</v>
       </c>
       <c r="B30" s="19"/>
@@ -2593,8 +2593,8 @@
       <c r="S32" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="T32" s="23"/>
-      <c r="U32" s="24"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="22"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19"/>
@@ -2609,8 +2609,8 @@
         <v>46169</v>
       </c>
       <c r="S33" s="19"/>
-      <c r="T33" s="25"/>
-      <c r="U33" s="26"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="24"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19"/>
@@ -2699,11 +2699,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2714,6 +2709,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D967F6C-BC49-4A89-87DB-CCBC1989327C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39B531E-A2BA-46D5-A057-E7082148FCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="108" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1108,13 +1108,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1127,15 +1136,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1438,36 +1438,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="J1" s="20" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="J1" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="R1" s="20" t="s">
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="R1" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20" t="s">
+      <c r="S1" s="18"/>
+      <c r="T1" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20" t="s">
+      <c r="U1" s="18"/>
+      <c r="V1" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="W1" s="20"/>
+      <c r="W1" s="18"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1594,10 +1594,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1760,16 +1760,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
       <c r="J8" s="1" t="s">
         <v>129</v>
       </c>
@@ -1824,14 +1824,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -1927,10 +1927,10 @@
       <c r="B12" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="16" t="s">
         <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1962,7 +1962,7 @@
       </c>
     </row>
     <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2003,7 +2003,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="17" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2027,7 +2027,7 @@
       <c r="H14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="22" t="s">
         <v>132</v>
       </c>
       <c r="R14" s="14">
@@ -2044,17 +2044,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="J15" s="27"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="J15" s="22"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2291,16 +2291,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
@@ -2532,21 +2532,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="20" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2556,17 +2556,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="20"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2576,51 +2576,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="20"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="T32" s="21"/>
-      <c r="U32" s="22"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="25"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="24"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="27"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2699,6 +2699,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2709,11 +2714,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39B531E-A2BA-46D5-A057-E7082148FCD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7129D9AD-DCEF-464E-B5E0-A686CC480805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5856" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="209">
   <si>
     <t>周一</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -563,6 +563,286 @@
   </si>
   <si>
     <t>复习任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一章绪论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性表的定义和基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性表的顺序表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>线性表的链式表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2 队列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1 栈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3 栈和队列的应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4 数组和特殊矩阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第四章 串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二叉树的概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二叉树的遍历和线索二叉树</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树、森林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树和二叉树的应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的存储及基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的遍历</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图的应用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查找的概念、顺序查找和折半查找</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树形查找</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B树和B+树</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>散列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交换排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归并排序、基数排序和计数排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各种内部排序算法的比较</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机系统概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>休息、反思、弹性调整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数制与编码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运算方法和运算电路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮点数的表示与运算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储器概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主存储器与CPU的连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外部存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高速缓冲存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚拟存储器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令系统</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寻址方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>程序的机器级代码表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CISC和RISC的基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU的功能和基本结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令执行过程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据通路的功能和基本结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制器的功能和工作原理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常和中断机制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指令流水线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多处理器基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总线概述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总线事务和定时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I/O系统基本概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I/O结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I/O方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据结构滚动复习计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机组成原理滚动复习计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统滚动复习计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>87、88、89</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90、91、92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>93、94、95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>96、97、98、99、100、101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5月开始，每月两篇小作文模板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到9月份全部背完</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据结构提前一天完结！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06、07、08、09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37、38、39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29、30、31、32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33、34、35、36</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -575,7 +855,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>备考的时间会过得很快的，现在只有246天，五一过完就不到230天，复习个一个月，六月就要应付期末考试（强度会降低）这时候已经剩下不到200天了，等到期末考试应付完，就得开始暑假的强化冲刺（有模拟考，而且要进行初步择校），结束后，估计也就不到120天，120天也就4个月，100天左右就到了国庆和中秋假期了，倒计时100天后就得忙着择校、报名、一周一次模考第话，也就模拟个9次而已，到时候还有政治课要上，得花时间听课、刷题背诵……所以时间是过得很快地，一会就结束了，所以现在200多天看似很多，但是其实只是刚好够用而已，一定一定要撑住不能松懈，当然在完成基本任务之后可以适当休息片刻，但不要放纵地去玩（不要出现考完期末就爽完好几天，放假先玩几天再学习之类的</t>
+      <t>备考的时间会过得很快的，现在只有246天，五一过完就不到230天，复习个一个月，六月就要应付期末考试（强度会降低）这时候已经剩下不到200天了，等到期末考试应付完，就得开始暑假的强化冲刺（有模拟考，而且要进行初步择校），结束后，估计也就不到120天，120天也就4个月，100天左右就到了国庆和中秋假期了，倒计时100天后就得忙着择校、报名、一周一次模考的话，也就模拟个9次而已，到时候还有政治课要上，得花时间听课、刷题背诵……所以时间是过得很快地，一会就结束了，所以现在200多天看似很多，但是其实只是刚好够用而已，一定一定要撑住不能松懈，当然在完成基本任务之后可以适当休息片刻，但不要放纵地去玩（不要出现考完期末就爽完好几天，放假先玩几天再学习之类的</t>
     </r>
     <r>
       <rPr>
@@ -590,283 +870,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>第一章绪论</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>线性表的定义和基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>线性表的顺序表示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>线性表的链式表示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2 队列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1 栈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.3 栈和队列的应用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.4 数组和特殊矩阵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第四章 串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>树的基本概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二叉树的概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二叉树的遍历和线索二叉树</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>树、森林</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>树和二叉树的应用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图的基本概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图的存储及基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图的遍历</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>图的应用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查找的概念、顺序查找和折半查找</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>树形查找</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B树和B+树</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>散列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排序的基本概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交换排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选择排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>归并排序、基数排序和计数排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各种内部排序算法的比较</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外部排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算机系统概述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>休息、反思、弹性调整</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数制与编码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运算方法和运算电路</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>浮点数的表示与运算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存储器概述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主存储器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主存储器与CPU的连接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>外部存储器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高速缓冲存储器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚拟存储器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指令系统</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寻址方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>程序的机器级代码表示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CISC和RISC的基本概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU的功能和基本结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指令执行过程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据通路的功能和基本结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>控制器的功能和工作原理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常和中断机制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指令流水线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多处理器基本概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总线概述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总线事务和定时</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I/O系统基本概念</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I/O结构</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I/O方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据结构滚动复习计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算机组成原理滚动复习计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作系统滚动复习计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>87、88、89</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>90、91、92</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>93、94、95</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>96、97、98、99、100、101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5月开始，每月两篇小作文模板</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到9月份全部背完</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据结构提前一天完结！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>06、07、08、09</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>37、38、39</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>29、30、31、32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>33、34、35、36</t>
+    <t>结束基础</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>408强化课、二轮过知识点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做套卷、三、四轮知识点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1457,15 +1469,15 @@
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
       <c r="R1" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="S1" s="18"/>
       <c r="T1" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U1" s="18"/>
       <c r="V1" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="W1" s="18"/>
     </row>
@@ -1572,13 +1584,13 @@
         <v>46139</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T3" s="14">
         <v>46170</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1624,13 +1636,13 @@
         <v>46140</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="T4" s="14">
         <v>46171</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1668,13 +1680,13 @@
         <v>46141</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T5" s="14">
         <v>46172</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1691,16 +1703,16 @@
         <v>56</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>197</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>198</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1712,13 +1724,13 @@
         <v>46142</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T6" s="14">
         <v>46173</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1726,13 +1738,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C7" s="16" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>36</v>
@@ -1750,13 +1762,13 @@
         <v>46143</v>
       </c>
       <c r="S7" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="T7" s="14">
         <v>46174</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1792,13 +1804,13 @@
         <v>46144</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T8" s="14">
         <v>46175</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1836,13 +1848,13 @@
         <v>46145</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T9" s="14">
         <v>46176</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1870,13 +1882,13 @@
         <v>46146</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="T10" s="14">
         <v>46177</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1890,13 +1902,13 @@
         <v>41</v>
       </c>
       <c r="D11" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>205</v>
-      </c>
       <c r="F11" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>42</v>
@@ -1911,13 +1923,13 @@
         <v>46147</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T11" s="14">
         <v>46178</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -1933,16 +1945,16 @@
       <c r="D12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="16" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -1952,23 +1964,23 @@
         <v>46148</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T12" s="14">
         <v>46179</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="16" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -1993,13 +2005,13 @@
         <v>46149</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="T13" s="14">
         <v>46180</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2034,13 +2046,13 @@
         <v>46150</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="T14" s="14">
         <v>46181</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2059,13 +2071,13 @@
         <v>46151</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="T15" s="14">
         <v>46182</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2092,22 +2104,22 @@
         <v>6</v>
       </c>
       <c r="J16" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="R16" s="14">
         <v>46152</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="T16" s="14">
         <v>46183</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2139,13 +2151,13 @@
         <v>46153</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T17" s="14">
         <v>46184</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2177,13 +2189,13 @@
         <v>46154</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T18" s="14">
         <v>46185</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2215,13 +2227,13 @@
         <v>46155</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T19" s="14">
         <v>46186</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -2249,17 +2261,23 @@
       <c r="H20" s="7" t="s">
         <v>88</v>
       </c>
+      <c r="I20" s="9">
+        <v>7.25</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>206</v>
+      </c>
       <c r="R20" s="14">
         <v>46156</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T20" s="14">
         <v>46187</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
@@ -2277,17 +2295,24 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
+      <c r="I21" s="9">
+        <v>9.1</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="K21" s="9"/>
       <c r="R21" s="14">
         <v>46157</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T21" s="14">
         <v>46188</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2301,17 +2326,24 @@
       <c r="F22" s="19"/>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
+      <c r="I22" s="9">
+        <v>10.1</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="K22" s="9"/>
       <c r="R22" s="14">
         <v>46158</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T22" s="14">
         <v>46189</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2337,17 +2369,20 @@
       <c r="H23" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
       <c r="R23" s="14">
         <v>46159</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T23" s="14">
         <v>46190</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2371,17 +2406,20 @@
       <c r="H24" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
       <c r="R24" s="14">
         <v>46160</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="T24" s="14">
         <v>46191</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2409,17 +2447,19 @@
       <c r="H25" s="7" t="s">
         <v>103</v>
       </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
       <c r="R25" s="14">
         <v>46161</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T25" s="14">
         <v>46192</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2447,17 +2487,19 @@
       <c r="H26" s="7" t="s">
         <v>107</v>
       </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
       <c r="R26" s="14">
         <v>46162</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="T26" s="14">
         <v>46193</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2483,17 +2525,19 @@
         <v>95</v>
       </c>
       <c r="H27" s="1"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
       <c r="R27" s="14">
         <v>46163</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T27" s="14">
         <v>46194</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2513,13 +2557,13 @@
         <v>46164</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T28" s="14">
         <v>46195</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2527,18 +2571,18 @@
         <v>46165</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="T29" s="14">
         <v>46196</v>
       </c>
       <c r="U29" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -2551,7 +2595,7 @@
         <v>46166</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T30" s="14">
         <v>46197</v>
@@ -2571,7 +2615,7 @@
         <v>46167</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T31" s="14">
         <v>46198</v>
@@ -2591,7 +2635,7 @@
         <v>46168</v>
       </c>
       <c r="S32" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T32" s="24"/>
       <c r="U32" s="25"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7129D9AD-DCEF-464E-B5E0-A686CC480805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483FCAC3-25C2-480E-B5A7-4462181B3183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5856" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1067,7 +1067,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1120,34 +1120,37 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1450,36 +1453,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="J1" s="18" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="J1" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="R1" s="18" t="s">
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="R1" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18" t="s">
+      <c r="S1" s="20"/>
+      <c r="T1" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18" t="s">
+      <c r="U1" s="20"/>
+      <c r="V1" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="W1" s="18"/>
+      <c r="W1" s="20"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1606,10 +1609,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1772,16 +1775,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
       <c r="J8" s="1" t="s">
         <v>129</v>
       </c>
@@ -1836,14 +1839,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2015,7 +2018,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2039,7 +2042,7 @@
       <c r="H14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="27" t="s">
         <v>132</v>
       </c>
       <c r="R14" s="14">
@@ -2056,17 +2059,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="J15" s="22"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="J15" s="27"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2123,7 +2126,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -2316,16 +2319,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="9">
         <v>10.1</v>
       </c>
@@ -2576,21 +2579,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="20" t="s">
+      <c r="U29" s="19" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2600,17 +2603,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="20"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2620,51 +2623,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="20"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="20" t="s">
+      <c r="S32" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="T32" s="24"/>
-      <c r="U32" s="25"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="22"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="20"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="27"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="24"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2743,11 +2746,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2758,6 +2756,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483FCAC3-25C2-480E-B5A7-4462181B3183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB5F0CC-476A-41D8-8F1D-FD97307D8413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5856" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1067,7 +1067,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1120,13 +1120,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1139,18 +1148,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1453,36 +1450,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="J1" s="20" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="J1" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="R1" s="20" t="s">
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="R1" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20" t="s">
+      <c r="S1" s="18"/>
+      <c r="T1" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20" t="s">
+      <c r="U1" s="18"/>
+      <c r="V1" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="W1" s="20"/>
+      <c r="W1" s="18"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1609,10 +1606,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1775,16 +1772,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
       <c r="J8" s="1" t="s">
         <v>129</v>
       </c>
@@ -1839,14 +1836,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2018,7 +2015,7 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2033,7 +2030,7 @@
       <c r="E14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G14" s="5" t="s">
@@ -2042,7 +2039,7 @@
       <c r="H14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="22" t="s">
         <v>132</v>
       </c>
       <c r="R14" s="14">
@@ -2059,17 +2056,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="J15" s="27"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="J15" s="22"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2126,7 +2123,7 @@
       </c>
     </row>
     <row r="17" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -2164,7 +2161,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -2319,16 +2316,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="9">
         <v>10.1</v>
       </c>
@@ -2579,21 +2576,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="20" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2603,17 +2600,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="20"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2623,51 +2620,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="20"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="T32" s="21"/>
-      <c r="U32" s="22"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="25"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="24"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="27"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2746,6 +2743,11 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2756,11 +2758,6 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB5F0CC-476A-41D8-8F1D-FD97307D8413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BDC0B3-5AAD-4B2C-83E7-BB5B8DA72C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5856" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2033,10 +2033,10 @@
       <c r="F14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>62</v>
       </c>
       <c r="J14" s="22" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -1120,22 +1120,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1148,6 +1139,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1450,36 +1450,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="J1" s="18" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="J1" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="R1" s="18" t="s">
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="R1" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18" t="s">
+      <c r="S1" s="20"/>
+      <c r="T1" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18" t="s">
+      <c r="U1" s="20"/>
+      <c r="V1" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="W1" s="18"/>
+      <c r="W1" s="20"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1606,10 +1606,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="21"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1772,16 +1772,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
       <c r="J8" s="1" t="s">
         <v>129</v>
       </c>
@@ -1836,14 +1836,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2039,7 +2039,7 @@
       <c r="H14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="27" t="s">
         <v>132</v>
       </c>
       <c r="R14" s="14">
@@ -2056,17 +2056,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="J15" s="22"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="J15" s="27"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2316,16 +2316,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
       <c r="I22" s="9">
         <v>10.1</v>
       </c>
@@ -2576,21 +2576,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="20" t="s">
+      <c r="U29" s="19" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2600,17 +2600,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="20"/>
+      <c r="U30" s="19"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2620,51 +2620,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="20"/>
+      <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="20" t="s">
+      <c r="S32" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="T32" s="24"/>
-      <c r="U32" s="25"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="22"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="20"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="27"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="24"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2743,11 +2743,6 @@
     <row r="78" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="S32:S33"/>
-    <mergeCell ref="U29:U31"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="T32:U33"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="J1:O1"/>
@@ -2758,6 +2753,11 @@
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:H34"/>
+    <mergeCell ref="S32:S33"/>
+    <mergeCell ref="U29:U31"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T32:U33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BDC0B3-5AAD-4B2C-83E7-BB5B8DA72C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788F05B3-DEB4-425F-BC5C-83AEDC06E4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5856" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2126,10 +2126,10 @@
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D17" s="5" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788F05B3-DEB4-425F-BC5C-83AEDC06E4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF335931-F590-4CD3-A2EE-DB3D1FEDEC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5856" yWindow="1104" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6132" yWindow="708" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2132,7 +2132,7 @@
       <c r="C17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E17" s="5" t="s">

--- a/Diary/408专业课安排.xlsx
+++ b/Diary/408专业课安排.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\study\My-Learning-Diary\Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF335931-F590-4CD3-A2EE-DB3D1FEDEC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBB5427-6E5C-455F-A29C-793A6C121E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6132" yWindow="708" windowWidth="14472" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -889,7 +889,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -932,6 +932,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1067,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1118,6 +1124,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1450,36 +1459,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="J1" s="20" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="J1" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="R1" s="20" t="s">
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="R1" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20" t="s">
+      <c r="S1" s="21"/>
+      <c r="T1" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20" t="s">
+      <c r="U1" s="21"/>
+      <c r="V1" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="W1" s="20"/>
+      <c r="W1" s="21"/>
     </row>
     <row r="2" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
@@ -1606,10 +1615,10 @@
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="26"/>
+      <c r="F4" s="27"/>
       <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
@@ -1772,16 +1781,16 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
       <c r="J8" s="1" t="s">
         <v>129</v>
       </c>
@@ -1836,14 +1845,14 @@
       <c r="H9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
       <c r="R9" s="14">
         <v>46145</v>
       </c>
@@ -2027,7 +2036,7 @@
       <c r="D14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="16" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -2039,7 +2048,7 @@
       <c r="H14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="28" t="s">
         <v>132</v>
       </c>
       <c r="R14" s="14">
@@ -2056,17 +2065,17 @@
       </c>
     </row>
     <row r="15" spans="1:23" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="J15" s="27"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="J15" s="28"/>
       <c r="R15" s="14">
         <v>46151</v>
       </c>
@@ -2135,16 +2144,16 @@
       <c r="D17" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>69</v>
       </c>
       <c r="R17" s="14">
@@ -2161,19 +2170,19 @@
       </c>
     </row>
     <row r="18" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="5" t="s">
@@ -2237,7 +2246,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -2252,7 +2261,7 @@
       <c r="E20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G20" s="7" t="s">
@@ -2316,16 +2325,16 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="I22" s="9">
         <v>10.1</v>
       </c>
@@ -2576,21 +2585,21 @@
       <c r="T29" s="14">
         <v>46196</v>
       </c>
-      <c r="U29" s="19" t="s">
+      <c r="U29" s="20" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
       <c r="R30" s="14">
         <v>46166</v>
       </c>
@@ -2600,17 +2609,17 @@
       <c r="T30" s="14">
         <v>46197</v>
       </c>
-      <c r="U30" s="19"/>
+      <c r="U30" s="20"/>
     </row>
     <row r="31" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
       <c r="R31" s="14">
         <v>46167</v>
       </c>
@@ -2620,51 +2629,51 @@
       <c r="T31" s="14">
         <v>46198</v>
       </c>
-      <c r="U31" s="19"/>
+      <c r="U31" s="20"/>
     </row>
     <row r="32" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
       <c r="R32" s="14">
         <v>46168</v>
       </c>
-      <c r="S32" s="19" t="s">
+      <c r="S32" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="T32" s="21"/>
-      <c r="U32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="23"/>
     </row>
     <row r="33" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
       <c r="R33" s="14">
         <v>46169</v>
       </c>
-      <c r="S33" s="19"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="24"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="25"/>
     </row>
     <row r="34" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:21" ht="27.6" customHeight="1" x14ac:dyDescent="0.25"/>
